--- a/mapping/aiuc_owasp_mapping.xlsx
+++ b/mapping/aiuc_owasp_mapping.xlsx
@@ -7,12 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIUC→OWASP (Control)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OWASP→AIUC (Control)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIUC→OWASP (Activity)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OWASP→AIUC (Activity)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIUC→OWASP (Control)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OWASP→AIUC (Control)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIUC→OWASP (Activity)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OWASP→AIUC (Activity)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'README'!$A$1:$D$120</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,11 +33,29 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -43,8 +64,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
+        <fgColor rgb="00D6E4F0"/>
+        <bgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -55,8 +88,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,13 +111,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -449,6 +503,1520 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D119"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AIUC-1 ↔ OWASP Agentic Top 10 Mapping Workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Workbook Overview</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>This workbook provides a bi-directional mapping between two AI governance frameworks: the AIUC-1 Standard (AI Use Case Controls) and the OWASP Top 10 for Agentic Applications (2026 edition).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>It is designed for compliance officers, risk managers, governance leads, auditors, and security program managers who need to understand how controls in one framework relate to risks in the other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>The workbook contains 5 sheets: this README plus 4 data sheets. The data sheets show mappings at two levels of detail (control-level and activity-level) in both directions (AIUC→OWASP and OWASP→AIUC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Tab-by-Tab Guide</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>▶ Sheet: AIUC→OWASP (Control)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Purpose: Shows which OWASP agentic risks each AIUC control addresses. Start here if you have an AIUC control and want to know which OWASP risks it covers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>How to read a row: Each row shows one AIUC control matched to one OWASP entry, with a score indicating how strong the connection is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>AIUC ID</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Unique identifier for the AIUC-1 control (e.g., A001, B003)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr"/>
+      <c r="D13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>AIUC Title</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Name of the AIUC control</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>AIUC Domain</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Domain category (e.g., Data &amp; Privacy, Security, Safety)</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>OWASP ID</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Identifier for the matched OWASP entry (e.g., ASI01)</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>OWASP Title</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Name of the matched OWASP agentic risk</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Composite similarity score from 0.0 to 1.0 (higher = stronger match)</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr"/>
+      <c r="D18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Tier: Direct (strong match) or Related (meaningful match)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr"/>
+      <c r="D19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Ref Bridge</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Reference Bridge sub-score: overlap in shared OWASP LLM Top 10 refs</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Semantic</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Semantic sub-score: NLP text similarity between descriptions</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Keyword sub-score: TF-IDF term overlap with synonym expansion</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr"/>
+      <c r="D22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>How the control relates to the risk (e.g., Prevents, Mitigates)</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr"/>
+      <c r="D23" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>▶ Sheet: OWASP→AIUC (Control)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Purpose: Shows which AIUC controls address each OWASP agentic risk. Start here if you have an OWASP risk and want to find relevant controls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>How to read a row: Each row shows one OWASP entry matched to one AIUC control, with a score and confidence tier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>OWASP ID</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Identifier for the OWASP entry (e.g., ASI01)</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr"/>
+      <c r="D29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>OWASP Title</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Name of the OWASP agentic risk</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr"/>
+      <c r="D30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>OWASP ranking (1 = highest priority risk)</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr"/>
+      <c r="D31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>AIUC ID</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Identifier for the matched AIUC control</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr"/>
+      <c r="D32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>AIUC Title</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Name of the matched AIUC control</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr"/>
+      <c r="D33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>AIUC Domain</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Domain category of the matched control</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr"/>
+      <c r="D34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Composite similarity score (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr"/>
+      <c r="D35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Tier: Direct or Related</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr"/>
+      <c r="D36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Ref Bridge</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Reference Bridge sub-score</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr"/>
+      <c r="D37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Semantic</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Semantic similarity sub-score</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr"/>
+      <c r="D38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Keyword overlap sub-score</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr"/>
+      <c r="D39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>How the control relates to the risk</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr"/>
+      <c r="D40" s="6" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>▶ Sheet: AIUC→OWASP (Activity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Purpose: Granular activity-level view. Each AIUC control has sub-activities; this sheet maps those individual activities to OWASP risks. Use this for detailed gap analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>How to read a row: Each row shows one AIUC activity (a specific action within a control) matched to one OWASP entry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr"/>
+      <c r="D45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Activity ID</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Unique identifier for the AIUC sub-activity</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr"/>
+      <c r="D46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Parent Control</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>The AIUC control this activity belongs to</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr"/>
+      <c r="D47" s="6" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>What this activity involves (truncated to 100 chars)</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr"/>
+      <c r="D48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>OWASP ID</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Identifier for the matched OWASP entry</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr"/>
+      <c r="D49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Composite similarity score (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr"/>
+      <c r="D50" s="6" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Tier: Direct or Related</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr"/>
+      <c r="D51" s="6" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>▶ Sheet: OWASP→AIUC (Activity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Purpose: Reverse activity-level view. Shows which AIUC activities address each OWASP risk. Use this to see the full set of actions relevant to a specific risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>How to read a row: Each row shows one OWASP entry matched to one AIUC activity, with its parent control and score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr"/>
+      <c r="D56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>OWASP ID</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Identifier for the OWASP entry</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr"/>
+      <c r="D57" s="6" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>OWASP Title</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Name of the OWASP agentic risk</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr"/>
+      <c r="D58" s="6" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Activity ID</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Identifier for the matched AIUC sub-activity</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr"/>
+      <c r="D59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Parent Control</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>The AIUC control this activity belongs to</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr"/>
+      <c r="D60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Composite similarity score (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr"/>
+      <c r="D61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Tier: Direct or Related</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr"/>
+      <c r="D62" s="6" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Understanding Confidence Tiers</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Every mapping is assigned a confidence tier based on its composite score. The tiers use color coding in the data sheets:</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Score Range</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>≥ 0.55</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Strong, well-supported connection. The control and risk share significant overlap in references, meaning, and terminology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Related</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>≥ 0.35</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Meaningful but less direct connection. The control is relevant to the risk but may only partially address it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Tangential</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>(not shown)</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>≥ 0.20</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>Weak connection. Filtered out of the data sheets to reduce noise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>(not shown)</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>&lt; 0.20</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>No meaningful connection. Filtered out of the data sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Relationship Types</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Each mapping includes a relationship type that describes how the AIUC control relates to the OWASP risk:</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr"/>
+      <c r="D74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Prevents</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>The control is designed to stop the risk from occurring. Preventative controls act before an incident happens.</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr"/>
+      <c r="D75" s="6" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Detects</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>The control is designed to identify when the risk is being exploited. Detective controls monitor for signs of an active threat.</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr"/>
+      <c r="D76" s="6" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Mitigates</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>The control reduces the impact or likelihood of the risk. It may not fully prevent the risk but limits its consequences.</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr"/>
+      <c r="D77" s="6" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Addresses</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>The control is relevant to the risk and provides meaningful coverage. Inferred from strong semantic or reference overlap.</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr"/>
+      <c r="D78" s="6" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Partially Addresses</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>The control has some relevance but does not fully cover the risk. May require additional controls for complete coverage.</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr"/>
+      <c r="D79" s="6" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Scoring Methodology</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n"/>
+      <c r="C81" s="3" t="n"/>
+      <c r="D81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Each mapping has a composite score from 0.0 to 1.0 that measures how strongly an AIUC control relates to an OWASP risk. The score combines three independent signals:</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>Composite Score = 0.45 × Reference Bridge + 0.35 × Semantic + 0.20 × Keyword</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>What It Measures</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Reference Bridge</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Jaccard overlap on shared OWASP LLM Top 10 references</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>If both the AIUC control and OWASP entry cite the same LLM vulnerabilities (e.g., LLM01, LLM06), they score higher. This is the strongest signal because shared references indicate the two frameworks are talking about the same underlying issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>Semantic Similarity</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Sentence-transformer NLP embeddings</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Measures how similar the descriptions and guidance text are in meaning, even if they use different words. Uses the all-MiniLM-L6-v2 model to convert text into numerical vectors and compute cosine similarity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>TF-IDF Keyword</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>TF-IDF with domain-specific synonym expansion</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Catches explicit term matches between the two texts. Includes synonym expansion so that 'authentication' matches 'access control' and similar domain-specific equivalences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Score range: 0.0 (no connection) to 1.0 (perfect match). In practice, scores above 0.55 indicate strong connections and scores between 0.35 and 0.55 indicate meaningful but weaker connections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>AIUC-1 Domains Quick Reference</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n"/>
+      <c r="C92" s="3" t="n"/>
+      <c r="D92" s="3" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>ID Range</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Focus</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>A — Data &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>A001–A007</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Data leakage, PII protection, IP rights</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>B — Security</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>B001–B009</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Adversarial robustness, input filtering, access control</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>C — Safety</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>C001–C012</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Harmful/out-of-scope outputs, vulnerability prevention</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>D — Reliability</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>D001–D004</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Hallucination prevention, unsafe tool call restriction</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>E — Accountability</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>E001–E017</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>Vendor management, audit logging, regulatory compliance</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>F — Society</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>F001–F002</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>Societal impact, responsible disclosure</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>OWASP Agentic Top 10 (2026) Quick Reference</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="n"/>
+      <c r="C101" s="3" t="n"/>
+      <c r="D101" s="3" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>ASI01</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>Agent Goal Hijack</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>Attackers manipulate an agent's objectives or decision pathways through prompt injection, deceptive outputs, or poisoned data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>ASI02</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>Tool Misuse and Exploitation</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>Agents misuse legitimate tools due to prompt injection, misalignment, or unsafe delegation, leading to data exfiltration or workflow hijacking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>ASI03</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>Identity &amp; Privilege Abuse</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>Agents inherit or escalate privileges beyond what is needed, enabling unauthorized access to systems and data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>ASI04</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>Agentic Supply Chain Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>Compromised tools, plugins, MCP servers, or dependencies introduce malicious capabilities into the agent's environment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>ASI05</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>Unexpected Code Execution</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>Agents generate and execute code that performs unintended or malicious actions, including arbitrary command execution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>ASI06</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>Memory &amp; Context Poisoning</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>Persistent corruption of an agent's stored context or long-term memory alters future behavior without direct attacker control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>ASI07</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>Multi-Agent Trust Issues</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>Agents in multi-agent systems trust peer messages without verification, enabling impersonation and coordinated manipulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>ASI08</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>Insufficient Monitoring &amp; Logging</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>Lack of comprehensive logging and behavioral monitoring makes it difficult to detect agent misuse or compromise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>ASI09</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>Lack of Human Oversight</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>Agents operate autonomously without adequate human review or approval gates for high-impact decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>ASI10</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>Rogue Agents</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>Agents develop autonomous misalignment, pursuing goals that diverge from intended objectives without active attacker involvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>How to Get Started</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="n"/>
+      <c r="C114" s="3" t="n"/>
+      <c r="D114" s="3" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>1. You're here! Read this README tab to understand the workbook structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>2. Choose your starting point: If you have an AIUC control, go to 'AIUC→OWASP (Control)'. If you have an OWASP risk, go to 'OWASP→AIUC (Control)'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>3. Look at Direct (green) mappings first — these are the strongest, most well-supported connections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>4. For more granular detail, use the Activity-level tabs to see which specific sub-activities within a control are relevant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>5. Use the Score and sub-scores (Ref Bridge, Semantic, Keyword) to understand why a mapping was made and how confident you can be in it.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="34">
+    <mergeCell ref="A116:D116"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A114:D114"/>
+    <mergeCell ref="A83:D83"/>
+    <mergeCell ref="A92:D92"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A82:D82"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A90:D90"/>
+    <mergeCell ref="A118:D118"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A42:D42"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K67"/>
@@ -468,57 +2036,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>AIUC ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>AIUC Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>AIUC Domain</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>OWASP ID</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>OWASP Title</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Ref Bridge</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Semantic</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Keyword</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
@@ -545,7 +2113,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -572,7 +2140,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -607,7 +2175,7 @@
       <c r="F4" t="n">
         <v>0.387</v>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -619,7 +2187,7 @@
         <v>0.639</v>
       </c>
       <c r="J4" t="n">
-        <v>0.065</v>
+        <v>0.064</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -654,9 +2222,9 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.362</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+        <v>0.363</v>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -668,7 +2236,7 @@
         <v>0.782</v>
       </c>
       <c r="J5" t="n">
-        <v>0.068</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -705,7 +2273,7 @@
       <c r="F6" t="n">
         <v>0.419</v>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -746,7 +2314,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -773,7 +2341,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -808,7 +2376,7 @@
       <c r="F9" t="n">
         <v>0.461</v>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -857,7 +2425,7 @@
       <c r="F10" t="n">
         <v>0.521</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -906,7 +2474,7 @@
       <c r="F11" t="n">
         <v>0.519</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -955,7 +2523,7 @@
       <c r="F12" t="n">
         <v>0.357</v>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -1004,7 +2572,7 @@
       <c r="F13" t="n">
         <v>0.453</v>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -1053,7 +2621,7 @@
       <c r="F14" t="n">
         <v>0.443</v>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -1102,7 +2670,7 @@
       <c r="F15" t="n">
         <v>0.432</v>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -1114,7 +2682,7 @@
         <v>0.844</v>
       </c>
       <c r="J15" t="n">
-        <v>0.122</v>
+        <v>0.121</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1151,7 +2719,7 @@
       <c r="F16" t="n">
         <v>0.389</v>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -1200,7 +2768,7 @@
       <c r="F17" t="n">
         <v>0.365</v>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -1249,7 +2817,7 @@
       <c r="F18" t="n">
         <v>0.431</v>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -1261,7 +2829,7 @@
         <v>0.849</v>
       </c>
       <c r="J18" t="n">
-        <v>0.107</v>
+        <v>0.106</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1296,9 +2864,9 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
+        <v>0.42</v>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -1310,7 +2878,7 @@
         <v>0.707</v>
       </c>
       <c r="J19" t="n">
-        <v>0.11</v>
+        <v>0.112</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1347,7 +2915,7 @@
       <c r="F20" t="n">
         <v>0.417</v>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -1396,7 +2964,7 @@
       <c r="F21" t="n">
         <v>0.369</v>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -1408,7 +2976,7 @@
         <v>0.38</v>
       </c>
       <c r="J21" t="n">
-        <v>0.055</v>
+        <v>0.057</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1437,7 +3005,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1472,7 +3040,7 @@
       <c r="F23" t="n">
         <v>0.484</v>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -1521,7 +3089,7 @@
       <c r="F24" t="n">
         <v>0.413</v>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -1533,7 +3101,7 @@
         <v>0.631</v>
       </c>
       <c r="J24" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1568,9 +3136,9 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
+        <v>0.399</v>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -1582,7 +3150,7 @@
         <v>0.667</v>
       </c>
       <c r="J25" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1617,9 +3185,9 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
+        <v>0.362</v>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -1631,7 +3199,7 @@
         <v>0.771</v>
       </c>
       <c r="J26" t="n">
-        <v>0.082</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1660,7 +3228,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1695,7 +3263,7 @@
       <c r="F28" t="n">
         <v>0.396</v>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -1744,7 +3312,7 @@
       <c r="F29" t="n">
         <v>0.38</v>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -1785,7 +3353,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1812,7 +3380,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1847,7 +3415,7 @@
       <c r="F32" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -1859,7 +3427,7 @@
         <v>0.888</v>
       </c>
       <c r="J32" t="n">
-        <v>0.114</v>
+        <v>0.113</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -1896,7 +3464,7 @@
       <c r="F33" t="n">
         <v>0.458</v>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -1945,7 +3513,7 @@
       <c r="F34" t="n">
         <v>0.397</v>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -1957,7 +3525,7 @@
         <v>0.791</v>
       </c>
       <c r="J34" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -1994,7 +3562,7 @@
       <c r="F35" t="n">
         <v>0.371</v>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -2006,7 +3574,7 @@
         <v>0.398</v>
       </c>
       <c r="J35" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2043,7 +3611,7 @@
       <c r="F36" t="n">
         <v>0.57</v>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -2084,7 +3652,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2111,7 +3679,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2138,7 +3706,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2165,7 +3733,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2192,7 +3760,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2219,7 +3787,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2254,7 +3822,7 @@
       <c r="F43" t="n">
         <v>0.5</v>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G43" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -2266,7 +3834,7 @@
         <v>0.759</v>
       </c>
       <c r="J43" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2303,7 +3871,7 @@
       <c r="F44" t="n">
         <v>0.428</v>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="G44" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -2352,7 +3920,7 @@
       <c r="F45" t="n">
         <v>0.362</v>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G45" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -2401,7 +3969,7 @@
       <c r="F46" t="n">
         <v>0.497</v>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -2413,7 +3981,7 @@
         <v>0.909</v>
       </c>
       <c r="J46" t="n">
-        <v>0.144</v>
+        <v>0.145</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2450,7 +4018,7 @@
       <c r="F47" t="n">
         <v>0.779</v>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G47" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -2462,7 +4030,7 @@
         <v>0.879</v>
       </c>
       <c r="J47" t="n">
-        <v>0.106</v>
+        <v>0.105</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2491,7 +4059,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2518,7 +4086,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2545,7 +4113,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2572,7 +4140,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2607,7 +4175,7 @@
       <c r="F52" t="n">
         <v>0.661</v>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G52" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -2656,7 +4224,7 @@
       <c r="F53" t="n">
         <v>0.752</v>
       </c>
-      <c r="G53" s="4" t="inlineStr">
+      <c r="G53" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -2668,7 +4236,7 @@
         <v>0.837</v>
       </c>
       <c r="J53" t="n">
-        <v>0.048</v>
+        <v>0.043</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -2697,7 +4265,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2724,7 +4292,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2757,9 +4325,9 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
+        <v>0.386</v>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -2771,7 +4339,7 @@
         <v>0.649</v>
       </c>
       <c r="J56" t="n">
-        <v>0.04</v>
+        <v>0.042</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -2808,7 +4376,7 @@
       <c r="F57" t="n">
         <v>0.358</v>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G57" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -2820,7 +4388,7 @@
         <v>0.662</v>
       </c>
       <c r="J57" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -2849,7 +4417,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2876,7 +4444,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2903,7 +4471,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2930,7 +4498,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2957,7 +4525,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2984,7 +4552,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3011,7 +4579,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3038,7 +4606,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3065,7 +4633,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3092,7 +4660,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3103,7 +4671,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3127,62 +4695,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>OWASP ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>OWASP Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>AIUC ID</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>AIUC Title</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>AIUC Domain</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Ref Bridge</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Semantic</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Keyword</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
@@ -3220,7 +4788,7 @@
       <c r="G2" t="n">
         <v>0.453</v>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -3270,9 +4838,9 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+        <v>0.42</v>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -3284,7 +4852,7 @@
         <v>0.707</v>
       </c>
       <c r="K3" t="n">
-        <v>0.11</v>
+        <v>0.112</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -3324,7 +4892,7 @@
       <c r="G4" t="n">
         <v>0.357</v>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -3376,7 +4944,7 @@
       <c r="G5" t="n">
         <v>0.779</v>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -3388,7 +4956,7 @@
         <v>0.879</v>
       </c>
       <c r="K5" t="n">
-        <v>0.106</v>
+        <v>0.105</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -3428,7 +4996,7 @@
       <c r="G6" t="n">
         <v>0.497</v>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -3440,7 +5008,7 @@
         <v>0.909</v>
       </c>
       <c r="K6" t="n">
-        <v>0.144</v>
+        <v>0.145</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -3478,9 +5046,9 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
+        <v>0.399</v>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -3492,7 +5060,7 @@
         <v>0.667</v>
       </c>
       <c r="K7" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -3532,7 +5100,7 @@
       <c r="G8" t="n">
         <v>0.387</v>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -3544,7 +5112,7 @@
         <v>0.639</v>
       </c>
       <c r="K8" t="n">
-        <v>0.065</v>
+        <v>0.064</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -3584,7 +5152,7 @@
       <c r="G9" t="n">
         <v>0.484</v>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -3636,7 +5204,7 @@
       <c r="G10" t="n">
         <v>0.752</v>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -3648,7 +5216,7 @@
         <v>0.837</v>
       </c>
       <c r="K10" t="n">
-        <v>0.048</v>
+        <v>0.043</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -3688,7 +5256,7 @@
       <c r="G11" t="n">
         <v>0.661</v>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -3740,7 +5308,7 @@
       <c r="G12" t="n">
         <v>0.461</v>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -3792,7 +5360,7 @@
       <c r="G13" t="n">
         <v>0.419</v>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -3844,7 +5412,7 @@
       <c r="G14" t="n">
         <v>0.358</v>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -3856,7 +5424,7 @@
         <v>0.662</v>
       </c>
       <c r="K14" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -3896,7 +5464,7 @@
       <c r="G15" t="n">
         <v>0.57</v>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -3948,7 +5516,7 @@
       <c r="G16" t="n">
         <v>0.521</v>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -4000,7 +5568,7 @@
       <c r="G17" t="n">
         <v>0.458</v>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -4052,7 +5620,7 @@
       <c r="G18" t="n">
         <v>0.432</v>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -4064,7 +5632,7 @@
         <v>0.844</v>
       </c>
       <c r="K18" t="n">
-        <v>0.122</v>
+        <v>0.121</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -4104,7 +5672,7 @@
       <c r="G19" t="n">
         <v>0.431</v>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -4116,7 +5684,7 @@
         <v>0.849</v>
       </c>
       <c r="K19" t="n">
-        <v>0.107</v>
+        <v>0.106</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -4156,7 +5724,7 @@
       <c r="G20" t="n">
         <v>0.38</v>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -4208,7 +5776,7 @@
       <c r="G21" t="n">
         <v>0.371</v>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -4220,7 +5788,7 @@
         <v>0.398</v>
       </c>
       <c r="K21" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -4260,7 +5828,7 @@
       <c r="G22" t="n">
         <v>0.519</v>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -4312,7 +5880,7 @@
       <c r="G23" t="n">
         <v>0.443</v>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -4364,7 +5932,7 @@
       <c r="G24" t="n">
         <v>0.417</v>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -4403,7 +5971,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -4441,7 +6009,7 @@
       <c r="G26" t="n">
         <v>0.369</v>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -4453,7 +6021,7 @@
         <v>0.38</v>
       </c>
       <c r="K26" t="n">
-        <v>0.055</v>
+        <v>0.057</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -4493,7 +6061,7 @@
       <c r="G27" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -4505,7 +6073,7 @@
         <v>0.888</v>
       </c>
       <c r="K27" t="n">
-        <v>0.114</v>
+        <v>0.113</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -4545,7 +6113,7 @@
       <c r="G28" t="n">
         <v>0.5</v>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -4557,7 +6125,7 @@
         <v>0.759</v>
       </c>
       <c r="K28" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -4597,7 +6165,7 @@
       <c r="G29" t="n">
         <v>0.428</v>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -4649,7 +6217,7 @@
       <c r="G30" t="n">
         <v>0.397</v>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -4661,7 +6229,7 @@
         <v>0.791</v>
       </c>
       <c r="K30" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -4699,9 +6267,9 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
+        <v>0.386</v>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -4713,7 +6281,7 @@
         <v>0.649</v>
       </c>
       <c r="K31" t="n">
-        <v>0.04</v>
+        <v>0.042</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -4753,7 +6321,7 @@
       <c r="G32" t="n">
         <v>0.365</v>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -4803,9 +6371,9 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.362</v>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
+        <v>0.363</v>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -4817,7 +6385,7 @@
         <v>0.782</v>
       </c>
       <c r="K33" t="n">
-        <v>0.068</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -4855,9 +6423,9 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
+        <v>0.362</v>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -4869,7 +6437,7 @@
         <v>0.771</v>
       </c>
       <c r="K34" t="n">
-        <v>0.082</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -4909,7 +6477,7 @@
       <c r="G35" t="n">
         <v>0.413</v>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -4921,7 +6489,7 @@
         <v>0.631</v>
       </c>
       <c r="K35" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -4961,7 +6529,7 @@
       <c r="G36" t="n">
         <v>0.396</v>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5013,7 +6581,7 @@
       <c r="G37" t="n">
         <v>0.389</v>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5065,7 +6633,7 @@
       <c r="G38" t="n">
         <v>0.362</v>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5090,7 +6658,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5108,32 +6676,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Activity ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Parent Control</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>OWASP ID</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
@@ -5160,7 +6728,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -5187,7 +6755,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -5214,7 +6782,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -5241,7 +6809,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -5271,7 +6839,7 @@
       <c r="E6" t="n">
         <v>0.427</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5299,9 +6867,9 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+        <v>0.403</v>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5331,7 +6899,7 @@
       <c r="E8" t="n">
         <v>0.427</v>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5359,9 +6927,9 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+        <v>0.383</v>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5391,7 +6959,7 @@
       <c r="E10" t="n">
         <v>0.365</v>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5421,7 +6989,7 @@
       <c r="E11" t="n">
         <v>0.427</v>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5449,9 +7017,9 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+        <v>0.403</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5481,7 +7049,7 @@
       <c r="E13" t="n">
         <v>0.372</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5511,7 +7079,7 @@
       <c r="E14" t="n">
         <v>0.365</v>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5541,7 +7109,7 @@
       <c r="E15" t="n">
         <v>0.439</v>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5571,7 +7139,7 @@
       <c r="E16" t="n">
         <v>0.459</v>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5601,7 +7169,7 @@
       <c r="E17" t="n">
         <v>0.419</v>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5631,7 +7199,7 @@
       <c r="E18" t="n">
         <v>0.419</v>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5658,7 +7226,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -5688,7 +7256,7 @@
       <c r="E20" t="n">
         <v>0.363</v>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5718,7 +7286,7 @@
       <c r="E21" t="n">
         <v>0.357</v>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5745,7 +7313,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -5775,7 +7343,7 @@
       <c r="E23" t="n">
         <v>0.379</v>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5805,7 +7373,7 @@
       <c r="E24" t="n">
         <v>0.359</v>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5835,7 +7403,7 @@
       <c r="E25" t="n">
         <v>0.399</v>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5865,7 +7433,7 @@
       <c r="E26" t="n">
         <v>0.36</v>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5895,7 +7463,7 @@
       <c r="E27" t="n">
         <v>0.501</v>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5925,7 +7493,7 @@
       <c r="E28" t="n">
         <v>0.461</v>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5955,7 +7523,7 @@
       <c r="E29" t="n">
         <v>0.461</v>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -5985,7 +7553,7 @@
       <c r="E30" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -6015,7 +7583,7 @@
       <c r="E31" t="n">
         <v>0.539</v>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6045,7 +7613,7 @@
       <c r="E32" t="n">
         <v>0.357</v>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6075,7 +7643,7 @@
       <c r="E33" t="n">
         <v>0.539</v>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6105,7 +7673,7 @@
       <c r="E34" t="n">
         <v>0.521</v>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6135,7 +7703,7 @@
       <c r="E35" t="n">
         <v>0.357</v>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6165,7 +7733,7 @@
       <c r="E36" t="n">
         <v>0.492</v>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6195,7 +7763,7 @@
       <c r="E37" t="n">
         <v>0.483</v>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6225,7 +7793,7 @@
       <c r="E38" t="n">
         <v>0.453</v>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6255,7 +7823,7 @@
       <c r="E39" t="n">
         <v>0.512</v>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6285,7 +7853,7 @@
       <c r="E40" t="n">
         <v>0.503</v>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6315,7 +7883,7 @@
       <c r="E41" t="n">
         <v>0.493</v>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6345,7 +7913,7 @@
       <c r="E42" t="n">
         <v>0.493</v>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6375,7 +7943,7 @@
       <c r="E43" t="n">
         <v>0.472</v>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6405,7 +7973,7 @@
       <c r="E44" t="n">
         <v>0.463</v>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6435,7 +8003,7 @@
       <c r="E45" t="n">
         <v>0.493</v>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6465,7 +8033,7 @@
       <c r="E46" t="n">
         <v>0.483</v>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6495,7 +8063,7 @@
       <c r="E47" t="n">
         <v>0.472</v>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6525,7 +8093,7 @@
       <c r="E48" t="n">
         <v>0.492</v>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F48" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6555,7 +8123,7 @@
       <c r="E49" t="n">
         <v>0.463</v>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F49" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6585,7 +8153,7 @@
       <c r="E50" t="n">
         <v>0.453</v>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F50" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6615,7 +8183,7 @@
       <c r="E51" t="n">
         <v>0.409</v>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6645,7 +8213,7 @@
       <c r="E52" t="n">
         <v>0.409</v>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F52" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6675,7 +8243,7 @@
       <c r="E53" t="n">
         <v>0.385</v>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F53" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6705,7 +8273,7 @@
       <c r="E54" t="n">
         <v>0.365</v>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F54" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6735,7 +8303,7 @@
       <c r="E55" t="n">
         <v>0.385</v>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6765,7 +8333,7 @@
       <c r="E56" t="n">
         <v>0.365</v>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F56" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6795,7 +8363,7 @@
       <c r="E57" t="n">
         <v>0.451</v>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F57" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6823,9 +8391,9 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
+        <v>0.44</v>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6855,7 +8423,7 @@
       <c r="E59" t="n">
         <v>0.417</v>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F59" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6885,7 +8453,7 @@
       <c r="E60" t="n">
         <v>0.389</v>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F60" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6915,7 +8483,7 @@
       <c r="E61" t="n">
         <v>0.451</v>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F61" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6943,9 +8511,9 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
+        <v>0.44</v>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -6975,7 +8543,7 @@
       <c r="E63" t="n">
         <v>0.437</v>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7005,7 +8573,7 @@
       <c r="E64" t="n">
         <v>0.389</v>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="F64" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7033,9 +8601,9 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
+        <v>0.46</v>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7065,7 +8633,7 @@
       <c r="E66" t="n">
         <v>0.431</v>
       </c>
-      <c r="F66" s="3" t="inlineStr">
+      <c r="F66" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7095,7 +8663,7 @@
       <c r="E67" t="n">
         <v>0.417</v>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7125,7 +8693,7 @@
       <c r="E68" t="n">
         <v>0.409</v>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="F68" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7155,7 +8723,7 @@
       <c r="E69" t="n">
         <v>0.451</v>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F69" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7183,9 +8751,9 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
+        <v>0.44</v>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7215,7 +8783,7 @@
       <c r="E71" t="n">
         <v>0.437</v>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F71" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7245,7 +8813,7 @@
       <c r="E72" t="n">
         <v>0.429</v>
       </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="F72" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7275,7 +8843,7 @@
       <c r="E73" t="n">
         <v>0.451</v>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F73" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7305,7 +8873,7 @@
       <c r="E74" t="n">
         <v>0.437</v>
       </c>
-      <c r="F74" s="3" t="inlineStr">
+      <c r="F74" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7333,9 +8901,9 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
+        <v>0.42</v>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7365,7 +8933,7 @@
       <c r="E76" t="n">
         <v>0.389</v>
       </c>
-      <c r="F76" s="3" t="inlineStr">
+      <c r="F76" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7392,7 +8960,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -7419,7 +8987,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F78" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -7449,7 +9017,7 @@
       <c r="E79" t="n">
         <v>0.544</v>
       </c>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="F79" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7479,7 +9047,7 @@
       <c r="E80" t="n">
         <v>0.433</v>
       </c>
-      <c r="F80" s="3" t="inlineStr">
+      <c r="F80" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7507,9 +9075,9 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
+        <v>0.419</v>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7537,9 +9105,9 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="F82" s="3" t="inlineStr">
+        <v>0.382</v>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7569,7 +9137,7 @@
       <c r="E83" t="n">
         <v>0.524</v>
       </c>
-      <c r="F83" s="3" t="inlineStr">
+      <c r="F83" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7599,7 +9167,7 @@
       <c r="E84" t="n">
         <v>0.413</v>
       </c>
-      <c r="F84" s="3" t="inlineStr">
+      <c r="F84" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7627,9 +9195,9 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
+        <v>0.399</v>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7657,9 +9225,9 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="F86" s="3" t="inlineStr">
+        <v>0.362</v>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7687,9 +9255,9 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.371</v>
-      </c>
-      <c r="F87" s="3" t="inlineStr">
+        <v>0.37</v>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7716,7 +9284,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F88" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -7744,9 +9312,9 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
+        <v>0.35</v>
+      </c>
+      <c r="F89" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7773,7 +9341,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F90" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -7803,7 +9371,7 @@
       <c r="E91" t="n">
         <v>0.396</v>
       </c>
-      <c r="F91" s="3" t="inlineStr">
+      <c r="F91" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7833,7 +9401,7 @@
       <c r="E92" t="n">
         <v>0.38</v>
       </c>
-      <c r="F92" s="3" t="inlineStr">
+      <c r="F92" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7863,7 +9431,7 @@
       <c r="E93" t="n">
         <v>0.4</v>
       </c>
-      <c r="F93" s="3" t="inlineStr">
+      <c r="F93" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7893,7 +9461,7 @@
       <c r="E94" t="n">
         <v>0.396</v>
       </c>
-      <c r="F94" s="3" t="inlineStr">
+      <c r="F94" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7923,7 +9491,7 @@
       <c r="E95" t="n">
         <v>0.416</v>
       </c>
-      <c r="F95" s="3" t="inlineStr">
+      <c r="F95" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7953,7 +9521,7 @@
       <c r="E96" t="n">
         <v>0.4</v>
       </c>
-      <c r="F96" s="3" t="inlineStr">
+      <c r="F96" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -7983,7 +9551,7 @@
       <c r="E97" t="n">
         <v>0.404</v>
       </c>
-      <c r="F97" s="3" t="inlineStr">
+      <c r="F97" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -8013,7 +9581,7 @@
       <c r="E98" t="n">
         <v>0.363</v>
       </c>
-      <c r="F98" s="3" t="inlineStr">
+      <c r="F98" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -8043,7 +9611,7 @@
       <c r="E99" t="n">
         <v>0.363</v>
       </c>
-      <c r="F99" s="3" t="inlineStr">
+      <c r="F99" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -8070,7 +9638,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F100" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -8097,7 +9665,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F101" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -8124,7 +9692,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F102" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -8154,7 +9722,7 @@
       <c r="E103" t="n">
         <v>0.618</v>
       </c>
-      <c r="F103" s="4" t="inlineStr">
+      <c r="F103" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -8184,7 +9752,7 @@
       <c r="E104" t="n">
         <v>0.383</v>
       </c>
-      <c r="F104" s="3" t="inlineStr">
+      <c r="F104" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -8214,7 +9782,7 @@
       <c r="E105" t="n">
         <v>0.355</v>
       </c>
-      <c r="F105" s="3" t="inlineStr">
+      <c r="F105" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -8244,7 +9812,7 @@
       <c r="E106" t="n">
         <v>0.618</v>
       </c>
-      <c r="F106" s="4" t="inlineStr">
+      <c r="F106" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -8274,7 +9842,7 @@
       <c r="E107" t="n">
         <v>0.375</v>
       </c>
-      <c r="F107" s="3" t="inlineStr">
+      <c r="F107" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -8304,7 +9872,7 @@
       <c r="E108" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="F108" s="4" t="inlineStr">
+      <c r="F108" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -8334,7 +9902,7 @@
       <c r="E109" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="F109" s="4" t="inlineStr">
+      <c r="F109" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -8364,7 +9932,7 @@
       <c r="E110" t="n">
         <v>0.458</v>
       </c>
-      <c r="F110" s="3" t="inlineStr">
+      <c r="F110" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -8394,7 +9962,7 @@
       <c r="E111" t="n">
         <v>0.478</v>
       </c>
-      <c r="F111" s="3" t="inlineStr">
+      <c r="F111" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -8424,7 +9992,7 @@
       <c r="E112" t="n">
         <v>0.458</v>
       </c>
-      <c r="F112" s="3" t="inlineStr">
+      <c r="F112" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -8454,7 +10022,7 @@
       <c r="E113" t="n">
         <v>0.437</v>
       </c>
-      <c r="F113" s="3" t="inlineStr">
+      <c r="F113" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -8484,7 +10052,7 @@
       <c r="E114" t="n">
         <v>0.411</v>
       </c>
-      <c r="F114" s="3" t="inlineStr">
+      <c r="F114" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -8514,7 +10082,7 @@
       <c r="E115" t="n">
         <v>0.353</v>
       </c>
-      <c r="F115" s="3" t="inlineStr">
+      <c r="F115" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -8544,7 +10112,7 @@
       <c r="E116" t="n">
         <v>0.397</v>
       </c>
-      <c r="F116" s="3" t="inlineStr">
+      <c r="F116" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -8574,7 +10142,7 @@
       <c r="E117" t="n">
         <v>0.371</v>
       </c>
-      <c r="F117" s="3" t="inlineStr">
+      <c r="F117" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -8604,7 +10172,7 @@
       <c r="E118" t="n">
         <v>0.397</v>
       </c>
-      <c r="F118" s="3" t="inlineStr">
+      <c r="F118" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -8634,7 +10202,7 @@
       <c r="E119" t="n">
         <v>0.391</v>
       </c>
-      <c r="F119" s="3" t="inlineStr">
+      <c r="F119" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -8664,7 +10232,7 @@
       <c r="E120" t="n">
         <v>0.59</v>
       </c>
-      <c r="F120" s="4" t="inlineStr">
+      <c r="F120" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -8694,7 +10262,7 @@
       <c r="E121" t="n">
         <v>0.61</v>
       </c>
-      <c r="F121" s="4" t="inlineStr">
+      <c r="F121" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -8724,7 +10292,7 @@
       <c r="E122" t="n">
         <v>0.57</v>
       </c>
-      <c r="F122" s="4" t="inlineStr">
+      <c r="F122" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -8751,7 +10319,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -8778,7 +10346,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F124" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -8805,7 +10373,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F125" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -8833,9 +10401,9 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.356</v>
-      </c>
-      <c r="F126" s="3" t="inlineStr">
+        <v>0.355</v>
+      </c>
+      <c r="F126" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -8862,7 +10430,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F127" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -8889,7 +10457,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F128" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -8916,7 +10484,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F129" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -8943,7 +10511,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F130" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -8970,7 +10538,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F131" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -8997,7 +10565,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F132" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -9024,7 +10592,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F133" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -9054,7 +10622,7 @@
       <c r="E134" t="n">
         <v>0.5</v>
       </c>
-      <c r="F134" s="3" t="inlineStr">
+      <c r="F134" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -9084,7 +10652,7 @@
       <c r="E135" t="n">
         <v>0.5</v>
       </c>
-      <c r="F135" s="3" t="inlineStr">
+      <c r="F135" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -9114,7 +10682,7 @@
       <c r="E136" t="n">
         <v>0.52</v>
       </c>
-      <c r="F136" s="3" t="inlineStr">
+      <c r="F136" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -9144,7 +10712,7 @@
       <c r="E137" t="n">
         <v>0.428</v>
       </c>
-      <c r="F137" s="3" t="inlineStr">
+      <c r="F137" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -9174,7 +10742,7 @@
       <c r="E138" t="n">
         <v>0.362</v>
       </c>
-      <c r="F138" s="3" t="inlineStr">
+      <c r="F138" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -9204,7 +10772,7 @@
       <c r="E139" t="n">
         <v>0.517</v>
       </c>
-      <c r="F139" s="3" t="inlineStr">
+      <c r="F139" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -9234,7 +10802,7 @@
       <c r="E140" t="n">
         <v>0.517</v>
       </c>
-      <c r="F140" s="3" t="inlineStr">
+      <c r="F140" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -9264,7 +10832,7 @@
       <c r="E141" t="n">
         <v>0.517</v>
       </c>
-      <c r="F141" s="3" t="inlineStr">
+      <c r="F141" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -9294,7 +10862,7 @@
       <c r="E142" t="n">
         <v>0.517</v>
       </c>
-      <c r="F142" s="3" t="inlineStr">
+      <c r="F142" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -9324,7 +10892,7 @@
       <c r="E143" t="n">
         <v>0.537</v>
       </c>
-      <c r="F143" s="3" t="inlineStr">
+      <c r="F143" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -9354,7 +10922,7 @@
       <c r="E144" t="n">
         <v>0.799</v>
       </c>
-      <c r="F144" s="4" t="inlineStr">
+      <c r="F144" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -9381,7 +10949,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F145" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -9408,7 +10976,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F146" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -9435,7 +11003,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F147" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -9462,7 +11030,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F148" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -9489,7 +11057,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F149" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -9516,7 +11084,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F150" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -9543,7 +11111,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F151" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -9570,7 +11138,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F152" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -9597,7 +11165,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F153" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -9624,7 +11192,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F154" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -9654,7 +11222,7 @@
       <c r="E155" t="n">
         <v>0.661</v>
       </c>
-      <c r="F155" s="4" t="inlineStr">
+      <c r="F155" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -9684,7 +11252,7 @@
       <c r="E156" t="n">
         <v>0.752</v>
       </c>
-      <c r="F156" s="4" t="inlineStr">
+      <c r="F156" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -9711,7 +11279,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F157" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -9738,7 +11306,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F158" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -9768,7 +11336,7 @@
       <c r="E159" t="n">
         <v>0.36</v>
       </c>
-      <c r="F159" s="3" t="inlineStr">
+      <c r="F159" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -9796,9 +11364,9 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="F160" s="3" t="inlineStr">
+        <v>0.406</v>
+      </c>
+      <c r="F160" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -9828,7 +11396,7 @@
       <c r="E161" t="n">
         <v>0.378</v>
       </c>
-      <c r="F161" s="3" t="inlineStr">
+      <c r="F161" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -9858,7 +11426,7 @@
       <c r="E162" t="n">
         <v>0.362</v>
       </c>
-      <c r="F162" s="3" t="inlineStr">
+      <c r="F162" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -9885,7 +11453,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F163" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -9912,7 +11480,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F164" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -9939,7 +11507,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F165" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -9966,7 +11534,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F166" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -9993,7 +11561,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F167" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10020,7 +11588,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F168" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10047,7 +11615,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F169" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10074,7 +11642,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F170" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10101,7 +11669,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F171" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10128,7 +11696,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F172" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10155,7 +11723,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F173" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10182,7 +11750,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F174" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10209,7 +11777,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F175" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10236,7 +11804,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F176" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10263,7 +11831,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F177" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10290,7 +11858,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F178" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10317,7 +11885,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F179" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10344,7 +11912,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F180" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10371,7 +11939,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F181" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10401,7 +11969,7 @@
       <c r="E182" t="n">
         <v>0.362</v>
       </c>
-      <c r="F182" s="3" t="inlineStr">
+      <c r="F182" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -10431,7 +11999,7 @@
       <c r="E183" t="n">
         <v>0.351</v>
       </c>
-      <c r="F183" s="3" t="inlineStr">
+      <c r="F183" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -10461,7 +12029,7 @@
       <c r="E184" t="n">
         <v>0.351</v>
       </c>
-      <c r="F184" s="3" t="inlineStr">
+      <c r="F184" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -10488,7 +12056,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F185" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10515,7 +12083,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F186" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10542,7 +12110,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F187" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10569,7 +12137,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F188" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10596,7 +12164,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F189" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10623,7 +12191,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F190" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10650,7 +12218,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F191" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10661,7 +12229,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10679,32 +12247,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>OWASP ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>OWASP Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Activity ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Parent Control</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
@@ -10734,7 +12302,7 @@
       <c r="E2" t="n">
         <v>0.493</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -10764,7 +12332,7 @@
       <c r="E3" t="n">
         <v>0.493</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -10794,7 +12362,7 @@
       <c r="E4" t="n">
         <v>0.493</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -10822,9 +12390,9 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+        <v>0.46</v>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -10854,7 +12422,7 @@
       <c r="E6" t="n">
         <v>0.453</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -10884,7 +12452,7 @@
       <c r="E7" t="n">
         <v>0.453</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -10912,9 +12480,9 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+        <v>0.44</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -10942,9 +12510,9 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+        <v>0.44</v>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -10972,9 +12540,9 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+        <v>0.44</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11002,9 +12570,9 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+        <v>0.42</v>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11034,7 +12602,7 @@
       <c r="E12" t="n">
         <v>0.357</v>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11064,7 +12632,7 @@
       <c r="E13" t="n">
         <v>0.357</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11094,7 +12662,7 @@
       <c r="E14" t="n">
         <v>0.351</v>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11124,7 +12692,7 @@
       <c r="E15" t="n">
         <v>0.351</v>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11154,7 +12722,7 @@
       <c r="E16" t="n">
         <v>0.799</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -11184,7 +12752,7 @@
       <c r="E17" t="n">
         <v>0.537</v>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11214,7 +12782,7 @@
       <c r="E18" t="n">
         <v>0.517</v>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11244,7 +12812,7 @@
       <c r="E19" t="n">
         <v>0.517</v>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11274,7 +12842,7 @@
       <c r="E20" t="n">
         <v>0.517</v>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11304,7 +12872,7 @@
       <c r="E21" t="n">
         <v>0.517</v>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11334,7 +12902,7 @@
       <c r="E22" t="n">
         <v>0.427</v>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11364,7 +12932,7 @@
       <c r="E23" t="n">
         <v>0.427</v>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11394,7 +12962,7 @@
       <c r="E24" t="n">
         <v>0.427</v>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11422,9 +12990,9 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
+        <v>0.419</v>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11452,9 +13020,9 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
+        <v>0.399</v>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11484,7 +13052,7 @@
       <c r="E27" t="n">
         <v>0.362</v>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11514,7 +13082,7 @@
       <c r="E28" t="n">
         <v>0.544</v>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11544,7 +13112,7 @@
       <c r="E29" t="n">
         <v>0.524</v>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11574,7 +13142,7 @@
       <c r="E30" t="n">
         <v>0.365</v>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11604,7 +13172,7 @@
       <c r="E31" t="n">
         <v>0.365</v>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11634,7 +13202,7 @@
       <c r="E32" t="n">
         <v>0.752</v>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -11664,7 +13232,7 @@
       <c r="E33" t="n">
         <v>0.661</v>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -11694,7 +13262,7 @@
       <c r="E34" t="n">
         <v>0.501</v>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11724,7 +13292,7 @@
       <c r="E35" t="n">
         <v>0.461</v>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11754,7 +13322,7 @@
       <c r="E36" t="n">
         <v>0.461</v>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11784,7 +13352,7 @@
       <c r="E37" t="n">
         <v>0.459</v>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11814,7 +13382,7 @@
       <c r="E38" t="n">
         <v>0.439</v>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11844,7 +13412,7 @@
       <c r="E39" t="n">
         <v>0.419</v>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11874,7 +13442,7 @@
       <c r="E40" t="n">
         <v>0.419</v>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11904,7 +13472,7 @@
       <c r="E41" t="n">
         <v>0.378</v>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11932,9 +13500,9 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.371</v>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
+        <v>0.37</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11962,9 +13530,9 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
+        <v>0.35</v>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -11994,7 +13562,7 @@
       <c r="E44" t="n">
         <v>0.61</v>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -12024,7 +13592,7 @@
       <c r="E45" t="n">
         <v>0.59</v>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -12054,7 +13622,7 @@
       <c r="E46" t="n">
         <v>0.57</v>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -12084,7 +13652,7 @@
       <c r="E47" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -12114,7 +13682,7 @@
       <c r="E48" t="n">
         <v>0.521</v>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F48" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12144,7 +13712,7 @@
       <c r="E49" t="n">
         <v>0.512</v>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F49" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12174,7 +13742,7 @@
       <c r="E50" t="n">
         <v>0.492</v>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F50" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12204,7 +13772,7 @@
       <c r="E51" t="n">
         <v>0.492</v>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12234,7 +13802,7 @@
       <c r="E52" t="n">
         <v>0.478</v>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F52" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12264,7 +13832,7 @@
       <c r="E53" t="n">
         <v>0.472</v>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F53" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12294,7 +13862,7 @@
       <c r="E54" t="n">
         <v>0.472</v>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F54" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12324,7 +13892,7 @@
       <c r="E55" t="n">
         <v>0.458</v>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12354,7 +13922,7 @@
       <c r="E56" t="n">
         <v>0.458</v>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F56" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12384,7 +13952,7 @@
       <c r="E57" t="n">
         <v>0.451</v>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F57" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12414,7 +13982,7 @@
       <c r="E58" t="n">
         <v>0.451</v>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F58" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12444,7 +14012,7 @@
       <c r="E59" t="n">
         <v>0.451</v>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F59" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12474,7 +14042,7 @@
       <c r="E60" t="n">
         <v>0.451</v>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F60" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12504,7 +14072,7 @@
       <c r="E61" t="n">
         <v>0.431</v>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F61" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12534,7 +14102,7 @@
       <c r="E62" t="n">
         <v>0.411</v>
       </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="F62" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12564,7 +14132,7 @@
       <c r="E63" t="n">
         <v>0.4</v>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12594,7 +14162,7 @@
       <c r="E64" t="n">
         <v>0.4</v>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="F64" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12624,7 +14192,7 @@
       <c r="E65" t="n">
         <v>0.391</v>
       </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="F65" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12654,7 +14222,7 @@
       <c r="E66" t="n">
         <v>0.383</v>
       </c>
-      <c r="F66" s="3" t="inlineStr">
+      <c r="F66" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12684,7 +14252,7 @@
       <c r="E67" t="n">
         <v>0.38</v>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12714,7 +14282,7 @@
       <c r="E68" t="n">
         <v>0.371</v>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="F68" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12744,7 +14312,7 @@
       <c r="E69" t="n">
         <v>0.539</v>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F69" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12774,7 +14342,7 @@
       <c r="E70" t="n">
         <v>0.539</v>
       </c>
-      <c r="F70" s="3" t="inlineStr">
+      <c r="F70" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12804,7 +14372,7 @@
       <c r="E71" t="n">
         <v>0.503</v>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F71" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12834,7 +14402,7 @@
       <c r="E72" t="n">
         <v>0.483</v>
       </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="F72" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12864,7 +14432,7 @@
       <c r="E73" t="n">
         <v>0.483</v>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F73" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12894,7 +14462,7 @@
       <c r="E74" t="n">
         <v>0.463</v>
       </c>
-      <c r="F74" s="3" t="inlineStr">
+      <c r="F74" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12924,7 +14492,7 @@
       <c r="E75" t="n">
         <v>0.463</v>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12954,7 +14522,7 @@
       <c r="E76" t="n">
         <v>0.437</v>
       </c>
-      <c r="F76" s="3" t="inlineStr">
+      <c r="F76" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -12984,7 +14552,7 @@
       <c r="E77" t="n">
         <v>0.437</v>
       </c>
-      <c r="F77" s="3" t="inlineStr">
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13014,7 +14582,7 @@
       <c r="E78" t="n">
         <v>0.437</v>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="F78" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13044,7 +14612,7 @@
       <c r="E79" t="n">
         <v>0.417</v>
       </c>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="F79" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13074,7 +14642,7 @@
       <c r="E80" t="n">
         <v>0.417</v>
       </c>
-      <c r="F80" s="3" t="inlineStr">
+      <c r="F80" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13104,7 +14672,7 @@
       <c r="E81" t="n">
         <v>0.399</v>
       </c>
-      <c r="F81" s="3" t="inlineStr">
+      <c r="F81" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13134,7 +14702,7 @@
       <c r="E82" t="n">
         <v>0.379</v>
       </c>
-      <c r="F82" s="3" t="inlineStr">
+      <c r="F82" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13164,7 +14732,7 @@
       <c r="E83" t="n">
         <v>0.372</v>
       </c>
-      <c r="F83" s="3" t="inlineStr">
+      <c r="F83" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13194,7 +14762,7 @@
       <c r="E84" t="n">
         <v>0.363</v>
       </c>
-      <c r="F84" s="3" t="inlineStr">
+      <c r="F84" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13224,7 +14792,7 @@
       <c r="E85" t="n">
         <v>0.359</v>
       </c>
-      <c r="F85" s="3" t="inlineStr">
+      <c r="F85" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13254,7 +14822,7 @@
       <c r="E86" t="n">
         <v>0.429</v>
       </c>
-      <c r="F86" s="3" t="inlineStr">
+      <c r="F86" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13284,7 +14852,7 @@
       <c r="E87" t="n">
         <v>0.409</v>
       </c>
-      <c r="F87" s="3" t="inlineStr">
+      <c r="F87" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13314,7 +14882,7 @@
       <c r="E88" t="n">
         <v>0.389</v>
       </c>
-      <c r="F88" s="3" t="inlineStr">
+      <c r="F88" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13344,7 +14912,7 @@
       <c r="E89" t="n">
         <v>0.389</v>
       </c>
-      <c r="F89" s="3" t="inlineStr">
+      <c r="F89" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13374,7 +14942,7 @@
       <c r="E90" t="n">
         <v>0.389</v>
       </c>
-      <c r="F90" s="3" t="inlineStr">
+      <c r="F90" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13404,7 +14972,7 @@
       <c r="E91" t="n">
         <v>0.618</v>
       </c>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="F91" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -13434,7 +15002,7 @@
       <c r="E92" t="n">
         <v>0.618</v>
       </c>
-      <c r="F92" s="4" t="inlineStr">
+      <c r="F92" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -13464,7 +15032,7 @@
       <c r="E93" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="F93" s="4" t="inlineStr">
+      <c r="F93" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -13494,7 +15062,7 @@
       <c r="E94" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="F94" s="4" t="inlineStr">
+      <c r="F94" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -13524,7 +15092,7 @@
       <c r="E95" t="n">
         <v>0.52</v>
       </c>
-      <c r="F95" s="3" t="inlineStr">
+      <c r="F95" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13554,7 +15122,7 @@
       <c r="E96" t="n">
         <v>0.5</v>
       </c>
-      <c r="F96" s="3" t="inlineStr">
+      <c r="F96" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13584,7 +15152,7 @@
       <c r="E97" t="n">
         <v>0.5</v>
       </c>
-      <c r="F97" s="3" t="inlineStr">
+      <c r="F97" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13614,7 +15182,7 @@
       <c r="E98" t="n">
         <v>0.437</v>
       </c>
-      <c r="F98" s="3" t="inlineStr">
+      <c r="F98" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13644,7 +15212,7 @@
       <c r="E99" t="n">
         <v>0.428</v>
       </c>
-      <c r="F99" s="3" t="inlineStr">
+      <c r="F99" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13672,9 +15240,9 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="F100" s="3" t="inlineStr">
+        <v>0.406</v>
+      </c>
+      <c r="F100" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13702,9 +15270,9 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="F101" s="3" t="inlineStr">
+        <v>0.403</v>
+      </c>
+      <c r="F101" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13732,9 +15300,9 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
+        <v>0.403</v>
+      </c>
+      <c r="F102" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13764,7 +15332,7 @@
       <c r="E103" t="n">
         <v>0.397</v>
       </c>
-      <c r="F103" s="3" t="inlineStr">
+      <c r="F103" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13794,7 +15362,7 @@
       <c r="E104" t="n">
         <v>0.397</v>
       </c>
-      <c r="F104" s="3" t="inlineStr">
+      <c r="F104" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13824,7 +15392,7 @@
       <c r="E105" t="n">
         <v>0.385</v>
       </c>
-      <c r="F105" s="3" t="inlineStr">
+      <c r="F105" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13854,7 +15422,7 @@
       <c r="E106" t="n">
         <v>0.385</v>
       </c>
-      <c r="F106" s="3" t="inlineStr">
+      <c r="F106" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13882,9 +15450,9 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="F107" s="3" t="inlineStr">
+        <v>0.383</v>
+      </c>
+      <c r="F107" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13912,9 +15480,9 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="F108" s="3" t="inlineStr">
+        <v>0.382</v>
+      </c>
+      <c r="F108" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13944,7 +15512,7 @@
       <c r="E109" t="n">
         <v>0.365</v>
       </c>
-      <c r="F109" s="3" t="inlineStr">
+      <c r="F109" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -13974,7 +15542,7 @@
       <c r="E110" t="n">
         <v>0.365</v>
       </c>
-      <c r="F110" s="3" t="inlineStr">
+      <c r="F110" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14004,7 +15572,7 @@
       <c r="E111" t="n">
         <v>0.363</v>
       </c>
-      <c r="F111" s="3" t="inlineStr">
+      <c r="F111" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14034,7 +15602,7 @@
       <c r="E112" t="n">
         <v>0.363</v>
       </c>
-      <c r="F112" s="3" t="inlineStr">
+      <c r="F112" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14053,18 +15621,18 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>E016.4</t>
+          <t>B007.2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>E016</t>
+          <t>B007</t>
         </is>
       </c>
       <c r="E113" t="n">
         <v>0.362</v>
       </c>
-      <c r="F113" s="3" t="inlineStr">
+      <c r="F113" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14083,18 +15651,18 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B007.2</t>
+          <t>E016.4</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>B007</t>
+          <t>E016</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="F114" s="3" t="inlineStr">
+        <v>0.362</v>
+      </c>
+      <c r="F114" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14124,7 +15692,7 @@
       <c r="E115" t="n">
         <v>0.36</v>
       </c>
-      <c r="F115" s="3" t="inlineStr">
+      <c r="F115" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14154,7 +15722,7 @@
       <c r="E116" t="n">
         <v>0.357</v>
       </c>
-      <c r="F116" s="3" t="inlineStr">
+      <c r="F116" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14182,9 +15750,9 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.356</v>
-      </c>
-      <c r="F117" s="3" t="inlineStr">
+        <v>0.355</v>
+      </c>
+      <c r="F117" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14214,7 +15782,7 @@
       <c r="E118" t="n">
         <v>0.433</v>
       </c>
-      <c r="F118" s="3" t="inlineStr">
+      <c r="F118" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14244,7 +15812,7 @@
       <c r="E119" t="n">
         <v>0.416</v>
       </c>
-      <c r="F119" s="3" t="inlineStr">
+      <c r="F119" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14274,7 +15842,7 @@
       <c r="E120" t="n">
         <v>0.413</v>
       </c>
-      <c r="F120" s="3" t="inlineStr">
+      <c r="F120" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14304,7 +15872,7 @@
       <c r="E121" t="n">
         <v>0.409</v>
       </c>
-      <c r="F121" s="3" t="inlineStr">
+      <c r="F121" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14334,7 +15902,7 @@
       <c r="E122" t="n">
         <v>0.409</v>
       </c>
-      <c r="F122" s="3" t="inlineStr">
+      <c r="F122" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14364,7 +15932,7 @@
       <c r="E123" t="n">
         <v>0.404</v>
       </c>
-      <c r="F123" s="3" t="inlineStr">
+      <c r="F123" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14394,7 +15962,7 @@
       <c r="E124" t="n">
         <v>0.396</v>
       </c>
-      <c r="F124" s="3" t="inlineStr">
+      <c r="F124" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14424,7 +15992,7 @@
       <c r="E125" t="n">
         <v>0.396</v>
       </c>
-      <c r="F125" s="3" t="inlineStr">
+      <c r="F125" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14454,7 +16022,7 @@
       <c r="E126" t="n">
         <v>0.375</v>
       </c>
-      <c r="F126" s="3" t="inlineStr">
+      <c r="F126" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14484,7 +16052,7 @@
       <c r="E127" t="n">
         <v>0.362</v>
       </c>
-      <c r="F127" s="3" t="inlineStr">
+      <c r="F127" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14514,7 +16082,7 @@
       <c r="E128" t="n">
         <v>0.36</v>
       </c>
-      <c r="F128" s="3" t="inlineStr">
+      <c r="F128" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14544,7 +16112,7 @@
       <c r="E129" t="n">
         <v>0.355</v>
       </c>
-      <c r="F129" s="3" t="inlineStr">
+      <c r="F129" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
@@ -14574,7 +16142,7 @@
       <c r="E130" t="n">
         <v>0.353</v>
       </c>
-      <c r="F130" s="3" t="inlineStr">
+      <c r="F130" s="10" t="inlineStr">
         <is>
           <t>Related</t>
         </is>
